--- a/SampleData/Modern/IncomeVerificationSampleDataRequest.xlsx
+++ b/SampleData/Modern/IncomeVerificationSampleDataRequest.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmohamed.EJADA\Downloads\MarketPLace\Income Verification\Income Verification\sampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salseriea.EJADA\Desktop\MP\sumayyah\marketplace_latest 13\marketplace_latest\SampleData\Modern\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66764CEB-7A88-484F-ADAA-0FF3739D0561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFFACB2-5596-46F0-AE16-43224C73660F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{50C03649-0042-4D5A-8BD6-E7242B0000F4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{50C03649-0042-4D5A-8BD6-E7242B0000F4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="IncomeVerification" sheetId="1" r:id="rId1"/>
+    <sheet name="FinancialInstitutions" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>Field Name</t>
   </si>
@@ -120,13 +121,71 @@
   </si>
   <si>
     <t>169290479232337152123533326058</t>
+  </si>
+  <si>
+    <t>Modern Financial Institutions - Sample Request Data</t>
+  </si>
+  <si>
+    <t>Sample Value 1</t>
+  </si>
+  <si>
+    <t>Sample Value 2</t>
+  </si>
+  <si>
+    <t>Sample Value 3</t>
+  </si>
+  <si>
+    <t>Sample Value 4</t>
+  </si>
+  <si>
+    <t>List Financial Institutions</t>
+  </si>
+  <si>
+    <t>financialInstitutionId</t>
+  </si>
+  <si>
+    <t>INMASARI</t>
+  </si>
+  <si>
+    <t>RJHISARI</t>
+  </si>
+  <si>
+    <t>financialInstitutionName</t>
+  </si>
+  <si>
+    <t>SAMA Model Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       List Financial Institution DataGroups</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">                 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FinancialInstitutionId</t>
+    </r>
+  </si>
+  <si>
+    <t>BSFRSARI</t>
+  </si>
+  <si>
+    <t>SAMAModelBank</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +229,42 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -209,7 +304,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -232,11 +327,128 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -272,8 +484,44 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -611,26 +859,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{054A50EE-133C-4E21-872E-6189E0B098F4}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.453125" customWidth="1"/>
-    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="1" max="1" width="37.44140625" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
     <col min="3" max="3" width="38" style="6" customWidth="1"/>
     <col min="4" max="4" width="38" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.7265625" customWidth="1"/>
+    <col min="5" max="5" width="37.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="10"/>
       <c r="B1" s="10"/>
       <c r="C1" s="11"/>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:6" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E1" s="25"/>
+    </row>
+    <row r="2" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -650,8 +898,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="26" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="14" t="s">
@@ -670,8 +918,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="16"/>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="26"/>
       <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
@@ -688,7 +936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5" s="9"/>
       <c r="C5" s="5"/>
@@ -696,7 +944,7 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>15</v>
       </c>
@@ -716,7 +964,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="12"/>
       <c r="B7" s="9"/>
       <c r="C7" s="5"/>
@@ -724,7 +972,7 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>16</v>
       </c>
@@ -744,7 +992,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="12"/>
       <c r="B9" s="9"/>
       <c r="C9" s="5"/>
@@ -765,6 +1013,106 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31FB7BD5-0C95-40C0-AE8E-A85E6F866F67}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+    </row>
+    <row r="2" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="30"/>
+      <c r="B4" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:A4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{0f1e79fc-1f4d-4187-a67d-c1c5354c13f8}" enabled="1" method="Standard" siteId="{e1304ad9-93ba-4557-8b20-8c1c1143b399}" contentBits="2" removed="0"/>
